--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/83.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/83.xlsx
@@ -426,13 +426,13 @@
         <v>-10.77343650301944</v>
       </c>
       <c r="E2">
-        <v>-9.76862695319776</v>
+        <v>-7.256451468968621</v>
       </c>
       <c r="F2">
-        <v>0.5059134178048443</v>
+        <v>-0.1551262231525387</v>
       </c>
       <c r="G2">
-        <v>-11.40799872553866</v>
+        <v>-9.828203083652905</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-10.17259280402977</v>
       </c>
       <c r="E3">
-        <v>-9.707175560913672</v>
+        <v>-7.377126244325021</v>
       </c>
       <c r="F3">
-        <v>0.3040162528809618</v>
+        <v>0.00716008126733009</v>
       </c>
       <c r="G3">
-        <v>-11.22897104386595</v>
+        <v>-9.288186895286991</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-9.484176728429473</v>
       </c>
       <c r="E4">
-        <v>-10.85524787676028</v>
+        <v>-8.644107230665041</v>
       </c>
       <c r="F4">
-        <v>0.5362603905564951</v>
+        <v>0.4045427777164385</v>
       </c>
       <c r="G4">
-        <v>-9.604062597916551</v>
+        <v>-7.571255214982471</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-8.775155727249285</v>
       </c>
       <c r="E5">
-        <v>-11.84552098733562</v>
+        <v>-9.824449452290311</v>
       </c>
       <c r="F5">
-        <v>0.425609233803614</v>
+        <v>0.2878149413660163</v>
       </c>
       <c r="G5">
-        <v>-9.912486262537211</v>
+        <v>-8.968510686378346</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-8.051305205032614</v>
       </c>
       <c r="E6">
-        <v>-12.24287193913865</v>
+        <v>-10.9250407181665</v>
       </c>
       <c r="F6">
-        <v>0.6803158643307826</v>
+        <v>0.1003762195971382</v>
       </c>
       <c r="G6">
-        <v>-9.005827155697011</v>
+        <v>-7.575217937992979</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-7.321287017069402</v>
       </c>
       <c r="E7">
-        <v>-12.60252787330184</v>
+        <v>-10.64199750726508</v>
       </c>
       <c r="F7">
-        <v>1.114018480391622</v>
+        <v>0.8057849654814728</v>
       </c>
       <c r="G7">
-        <v>-8.873279533395671</v>
+        <v>-7.705911654792327</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-6.582796871810277</v>
       </c>
       <c r="E8">
-        <v>-12.82332268049382</v>
+        <v>-11.59702097616471</v>
       </c>
       <c r="F8">
-        <v>0.8529366417018516</v>
+        <v>0.8976256552237218</v>
       </c>
       <c r="G8">
-        <v>-7.959794081653494</v>
+        <v>-7.830239192519656</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-5.837909967649829</v>
       </c>
       <c r="E9">
-        <v>-14.15107125954277</v>
+        <v>-12.52869110460677</v>
       </c>
       <c r="F9">
-        <v>0.9598827184655619</v>
+        <v>1.007241860160863</v>
       </c>
       <c r="G9">
-        <v>-8.279341179286106</v>
+        <v>-6.478632833564791</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-5.071009478186622</v>
       </c>
       <c r="E10">
-        <v>-15.33967341775803</v>
+        <v>-13.87365241335888</v>
       </c>
       <c r="F10">
-        <v>1.061825868242399</v>
+        <v>1.205852835310209</v>
       </c>
       <c r="G10">
-        <v>-6.426902248968139</v>
+        <v>-4.866741452675806</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-4.284666523168491</v>
       </c>
       <c r="E11">
-        <v>-15.64391894396337</v>
+        <v>-13.92650876197641</v>
       </c>
       <c r="F11">
-        <v>1.375480408501097</v>
+        <v>0.9236950382977707</v>
       </c>
       <c r="G11">
-        <v>-6.100714196983748</v>
+        <v>-4.447474102309267</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-3.480561526701468</v>
       </c>
       <c r="E12">
-        <v>-15.85537603775153</v>
+        <v>-15.63551862467914</v>
       </c>
       <c r="F12">
-        <v>1.416496808005064</v>
+        <v>1.514000830100924</v>
       </c>
       <c r="G12">
-        <v>-5.912165386340098</v>
+        <v>-5.212961615718326</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-2.658014378011768</v>
       </c>
       <c r="E13">
-        <v>-16.41356027241099</v>
+        <v>-13.62041108990194</v>
       </c>
       <c r="F13">
-        <v>1.62792154771623</v>
+        <v>1.071404121618977</v>
       </c>
       <c r="G13">
-        <v>-5.008906209768729</v>
+        <v>-4.437078989315956</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-1.837761669440919</v>
       </c>
       <c r="E14">
-        <v>-18.69218423816854</v>
+        <v>-16.82178861878045</v>
       </c>
       <c r="F14">
-        <v>1.473472212018913</v>
+        <v>1.699102793791571</v>
       </c>
       <c r="G14">
-        <v>-4.559489721176048</v>
+        <v>-3.100108552190209</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-1.032586224588808</v>
       </c>
       <c r="E15">
-        <v>-18.06149913464628</v>
+        <v>-16.53455656942193</v>
       </c>
       <c r="F15">
-        <v>1.64916696257185</v>
+        <v>2.000809856624194</v>
       </c>
       <c r="G15">
-        <v>-4.226134338099135</v>
+        <v>-2.384110384047715</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-0.2547323406826932</v>
       </c>
       <c r="E16">
-        <v>-18.28226224252021</v>
+        <v>-16.97722396061972</v>
       </c>
       <c r="F16">
-        <v>1.90641148182851</v>
+        <v>1.146489202775877</v>
       </c>
       <c r="G16">
-        <v>-3.009475746961582</v>
+        <v>-2.087353081907446</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>0.476269359021405</v>
       </c>
       <c r="E17">
-        <v>-19.11757097255306</v>
+        <v>-18.83399340171873</v>
       </c>
       <c r="F17">
-        <v>1.846032693802381</v>
+        <v>1.434842457329514</v>
       </c>
       <c r="G17">
-        <v>-3.760416723271083</v>
+        <v>-1.323914796187196</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>1.149927803417989</v>
       </c>
       <c r="E18">
-        <v>-20.97496081459112</v>
+        <v>-19.49423585508906</v>
       </c>
       <c r="F18">
-        <v>2.071579339161521</v>
+        <v>1.590194505398631</v>
       </c>
       <c r="G18">
-        <v>-2.536057803209184</v>
+        <v>-2.263388030412652</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>1.750799561880803</v>
       </c>
       <c r="E19">
-        <v>-22.18091608520377</v>
+        <v>-19.31061981950005</v>
       </c>
       <c r="F19">
-        <v>1.898728924432713</v>
+        <v>1.500536162407858</v>
       </c>
       <c r="G19">
-        <v>-2.85813084708826</v>
+        <v>-1.55401426389424</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>2.261986326484487</v>
       </c>
       <c r="E20">
-        <v>-22.31534836459548</v>
+        <v>-20.50146810082311</v>
       </c>
       <c r="F20">
-        <v>2.374931872440285</v>
+        <v>2.180243736843483</v>
       </c>
       <c r="G20">
-        <v>-2.349819753351944</v>
+        <v>-2.085257506581087</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>2.671725293845546</v>
       </c>
       <c r="E21">
-        <v>-22.74809839771647</v>
+        <v>-19.35826389453475</v>
       </c>
       <c r="F21">
-        <v>1.98729926145958</v>
+        <v>2.443688464759089</v>
       </c>
       <c r="G21">
-        <v>-2.601053743781695</v>
+        <v>-0.6051390803372535</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>2.962150441774349</v>
       </c>
       <c r="E22">
-        <v>-24.41015251343367</v>
+        <v>-22.28349960689953</v>
       </c>
       <c r="F22">
-        <v>2.04800746031612</v>
+        <v>2.126364477894318</v>
       </c>
       <c r="G22">
-        <v>-1.755007415220011</v>
+        <v>-0.01840447332114244</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>3.1230618123174</v>
       </c>
       <c r="E23">
-        <v>-23.68818243086479</v>
+        <v>-22.79058454085643</v>
       </c>
       <c r="F23">
-        <v>2.316508961219724</v>
+        <v>1.737567843065764</v>
       </c>
       <c r="G23">
-        <v>-2.071621369504829</v>
+        <v>-0.5315026159072445</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>3.147366534362964</v>
       </c>
       <c r="E24">
-        <v>-24.05357141312169</v>
+        <v>-22.77509263127619</v>
       </c>
       <c r="F24">
-        <v>2.407396260000879</v>
+        <v>2.321339264261815</v>
       </c>
       <c r="G24">
-        <v>-1.056220773336188</v>
+        <v>0.2755852127482961</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>3.029619216209765</v>
       </c>
       <c r="E25">
-        <v>-22.68488090056939</v>
+        <v>-22.15770765591446</v>
       </c>
       <c r="F25">
-        <v>2.096229721735336</v>
+        <v>2.186352090559333</v>
       </c>
       <c r="G25">
-        <v>-1.891961373634121</v>
+        <v>-1.167895406012423</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>2.774752646085226</v>
       </c>
       <c r="E26">
-        <v>-23.77559103616084</v>
+        <v>-25.14911343047932</v>
       </c>
       <c r="F26">
-        <v>2.172010049789113</v>
+        <v>1.922596956284301</v>
       </c>
       <c r="G26">
-        <v>-1.226902569704393</v>
+        <v>-0.009439516000796068</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>2.387996862737896</v>
       </c>
       <c r="E27">
-        <v>-24.04133094787895</v>
+        <v>-23.01660973552728</v>
       </c>
       <c r="F27">
-        <v>2.127004295084155</v>
+        <v>2.265323586032721</v>
       </c>
       <c r="G27">
-        <v>-0.2885482998712106</v>
+        <v>0.1114847809121626</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>1.883515610152114</v>
       </c>
       <c r="E28">
-        <v>-23.689486631379</v>
+        <v>-23.28845855868174</v>
       </c>
       <c r="F28">
-        <v>2.327458703919072</v>
+        <v>1.691607113693796</v>
       </c>
       <c r="G28">
-        <v>-1.23354683460171</v>
+        <v>-0.2604384576972589</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>1.279381302069847</v>
       </c>
       <c r="E29">
-        <v>-22.99503155688073</v>
+        <v>-24.26973811987783</v>
       </c>
       <c r="F29">
-        <v>1.797058172073332</v>
+        <v>2.244673644601306</v>
       </c>
       <c r="G29">
-        <v>-1.702833217521097</v>
+        <v>0.6410628191927565</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>0.5918456785186574</v>
       </c>
       <c r="E30">
-        <v>-23.1835836291381</v>
+        <v>-21.5512272459632</v>
       </c>
       <c r="F30">
-        <v>2.377817384618216</v>
+        <v>2.343104134657699</v>
       </c>
       <c r="G30">
-        <v>-2.010359724300616</v>
+        <v>0.664422028517854</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-0.1551388794138167</v>
       </c>
       <c r="E31">
-        <v>-22.40903796334016</v>
+        <v>-23.94840213276755</v>
       </c>
       <c r="F31">
-        <v>2.490618422151306</v>
+        <v>2.045239142375932</v>
       </c>
       <c r="G31">
-        <v>-1.67079706833757</v>
+        <v>-0.157798303797695</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-0.9468653951247774</v>
       </c>
       <c r="E32">
-        <v>-22.69558621312352</v>
+        <v>-22.18467471863014</v>
       </c>
       <c r="F32">
-        <v>2.247660513957825</v>
+        <v>2.181084684684582</v>
       </c>
       <c r="G32">
-        <v>-1.802801761170469</v>
+        <v>0.3605967116512409</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-1.768609235827789</v>
       </c>
       <c r="E33">
-        <v>-22.08226780742068</v>
+        <v>-21.13578504049952</v>
       </c>
       <c r="F33">
-        <v>2.104078568252254</v>
+        <v>2.790234993175549</v>
       </c>
       <c r="G33">
-        <v>-2.834377682843989</v>
+        <v>-0.4978641626827099</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-2.600278734192715</v>
       </c>
       <c r="E34">
-        <v>-22.75571076252336</v>
+        <v>-21.46457942430044</v>
       </c>
       <c r="F34">
-        <v>2.340722240960878</v>
+        <v>2.357069253420044</v>
       </c>
       <c r="G34">
-        <v>-2.925368026990858</v>
+        <v>-0.4700489590617534</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-3.43801200069932</v>
       </c>
       <c r="E35">
-        <v>-21.41289142197689</v>
+        <v>-20.36582671887136</v>
       </c>
       <c r="F35">
-        <v>2.553247656283275</v>
+        <v>2.159893115830086</v>
       </c>
       <c r="G35">
-        <v>-2.875431758076491</v>
+        <v>-1.103247072721536</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-4.269827499334732</v>
       </c>
       <c r="E36">
-        <v>-20.64302819830289</v>
+        <v>-20.09130156757837</v>
       </c>
       <c r="F36">
-        <v>2.245180430494247</v>
+        <v>2.330681545456992</v>
       </c>
       <c r="G36">
-        <v>-3.570497346774173</v>
+        <v>-2.224181239591063</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-5.082855155360077</v>
       </c>
       <c r="E37">
-        <v>-19.94759044494495</v>
+        <v>-19.44491624467152</v>
       </c>
       <c r="F37">
-        <v>2.312358068015357</v>
+        <v>2.435274235230359</v>
       </c>
       <c r="G37">
-        <v>-4.001914399269837</v>
+        <v>-1.21537856068219</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-5.874857172411565</v>
       </c>
       <c r="E38">
-        <v>-18.87498967691017</v>
+        <v>-18.47238116678423</v>
       </c>
       <c r="F38">
-        <v>2.535975759569492</v>
+        <v>1.979984123836165</v>
       </c>
       <c r="G38">
-        <v>-3.506938182965706</v>
+        <v>-1.647788776839635</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-6.633220987472399</v>
       </c>
       <c r="E39">
-        <v>-17.64645543489527</v>
+        <v>-18.44899159853462</v>
       </c>
       <c r="F39">
-        <v>2.512454559313385</v>
+        <v>2.666533307826489</v>
       </c>
       <c r="G39">
-        <v>-4.044276139990351</v>
+        <v>-1.554924663917539</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-7.349959225316692</v>
       </c>
       <c r="E40">
-        <v>-17.17538092624736</v>
+        <v>-18.22639445868758</v>
       </c>
       <c r="F40">
-        <v>2.329815258321247</v>
+        <v>2.530950660699803</v>
       </c>
       <c r="G40">
-        <v>-3.851824196155899</v>
+        <v>-1.416951057477334</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-8.023564192463875</v>
       </c>
       <c r="E41">
-        <v>-16.97487821108375</v>
+        <v>-16.52366558943348</v>
       </c>
       <c r="F41">
-        <v>2.944849034288072</v>
+        <v>2.499914775874936</v>
       </c>
       <c r="G41">
-        <v>-4.520296172536616</v>
+        <v>-2.559834141272229</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-8.640639166372509</v>
       </c>
       <c r="E42">
-        <v>-17.43563685594219</v>
+        <v>-15.20672647784085</v>
       </c>
       <c r="F42">
-        <v>3.109293138017726</v>
+        <v>2.59957738913354</v>
       </c>
       <c r="G42">
-        <v>-4.357175662180107</v>
+        <v>-1.560698255338028</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-9.201049816933125</v>
       </c>
       <c r="E43">
-        <v>-15.73548468839846</v>
+        <v>-16.28392364699341</v>
       </c>
       <c r="F43">
-        <v>3.154970384030831</v>
+        <v>2.458492947656617</v>
       </c>
       <c r="G43">
-        <v>-4.158102627267112</v>
+        <v>-3.315860115530051</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-9.706160745952262</v>
       </c>
       <c r="E44">
-        <v>-14.39460353472727</v>
+        <v>-15.11269271507157</v>
       </c>
       <c r="F44">
-        <v>3.040338582459493</v>
+        <v>2.325849658708986</v>
       </c>
       <c r="G44">
-        <v>-4.389940131382274</v>
+        <v>-1.614928301816829</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-10.14579151680332</v>
       </c>
       <c r="E45">
-        <v>-15.51643334369943</v>
+        <v>-15.04170435652733</v>
       </c>
       <c r="F45">
-        <v>3.096366930335909</v>
+        <v>2.931230747121207</v>
       </c>
       <c r="G45">
-        <v>-5.224598183288864</v>
+        <v>-1.827233587250291</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-10.52790856381443</v>
       </c>
       <c r="E46">
-        <v>-14.12457062964988</v>
+        <v>-14.01873566361662</v>
       </c>
       <c r="F46">
-        <v>2.980178345849695</v>
+        <v>2.508325837991835</v>
       </c>
       <c r="G46">
-        <v>-4.961939500203089</v>
+        <v>-3.206158567995222</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-10.85551346427358</v>
       </c>
       <c r="E47">
-        <v>-13.78793292886768</v>
+        <v>-12.37153041417057</v>
       </c>
       <c r="F47">
-        <v>3.319759735650052</v>
+        <v>2.651022492090675</v>
       </c>
       <c r="G47">
-        <v>-5.065738345041398</v>
+        <v>-3.791529230249153</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-11.1243698187341</v>
       </c>
       <c r="E48">
-        <v>-12.98618471970568</v>
+        <v>-11.48365515785668</v>
       </c>
       <c r="F48">
-        <v>3.309934424150665</v>
+        <v>3.130578145521233</v>
       </c>
       <c r="G48">
-        <v>-4.829077376075518</v>
+        <v>-4.293063637266581</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-11.34677982258833</v>
       </c>
       <c r="E49">
-        <v>-12.21549278528828</v>
+        <v>-11.27532271113381</v>
       </c>
       <c r="F49">
-        <v>3.149980126691281</v>
+        <v>2.616402680779169</v>
       </c>
       <c r="G49">
-        <v>-5.372116092518788</v>
+        <v>-3.460060858129625</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-11.52286013147182</v>
       </c>
       <c r="E50">
-        <v>-11.65378539785085</v>
+        <v>-10.99028697166901</v>
       </c>
       <c r="F50">
-        <v>3.472657039550238</v>
+        <v>3.199649895317209</v>
       </c>
       <c r="G50">
-        <v>-5.462262247553143</v>
+        <v>-4.151408704186706</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-11.65160439703249</v>
       </c>
       <c r="E51">
-        <v>-12.15514181218805</v>
+        <v>-11.30726203830991</v>
       </c>
       <c r="F51">
-        <v>3.667872549216881</v>
+        <v>2.513528311924053</v>
       </c>
       <c r="G51">
-        <v>-5.740847965228353</v>
+        <v>-3.545234573763995</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-11.74587526688094</v>
       </c>
       <c r="E52">
-        <v>-11.01444185202593</v>
+        <v>-12.60106517619736</v>
       </c>
       <c r="F52">
-        <v>3.309071304426751</v>
+        <v>3.119070938339649</v>
       </c>
       <c r="G52">
-        <v>-5.635238251980063</v>
+        <v>-4.063374677206407</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-11.79825322658054</v>
       </c>
       <c r="E53">
-        <v>-11.28536233800881</v>
+        <v>-10.33668326119394</v>
       </c>
       <c r="F53">
-        <v>3.500527096250141</v>
+        <v>3.108189294994665</v>
       </c>
       <c r="G53">
-        <v>-5.231351696188978</v>
+        <v>-3.084201380874011</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-11.81186730805132</v>
       </c>
       <c r="E54">
-        <v>-9.749489622041345</v>
+        <v>-10.49060609271465</v>
       </c>
       <c r="F54">
-        <v>3.43590556007655</v>
+        <v>3.071382385813937</v>
       </c>
       <c r="G54">
-        <v>-6.308811779036796</v>
+        <v>-4.492855060561597</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-11.79782759430938</v>
       </c>
       <c r="E55">
-        <v>-10.57770223330418</v>
+        <v>-9.738843179649312</v>
       </c>
       <c r="F55">
-        <v>3.26059723376698</v>
+        <v>3.024040664883705</v>
       </c>
       <c r="G55">
-        <v>-5.877934345464033</v>
+        <v>-3.844117246140476</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-11.74814466385804</v>
       </c>
       <c r="E56">
-        <v>-9.967576401776741</v>
+        <v>-9.217443739354161</v>
       </c>
       <c r="F56">
-        <v>3.342352884239711</v>
+        <v>3.077414721645846</v>
       </c>
       <c r="G56">
-        <v>-6.490802398967151</v>
+        <v>-3.825310036931876</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-11.67347831643862</v>
       </c>
       <c r="E57">
-        <v>-8.696075998377067</v>
+        <v>-7.891846185458856</v>
       </c>
       <c r="F57">
-        <v>3.679325910397339</v>
+        <v>3.038485646538429</v>
       </c>
       <c r="G57">
-        <v>-6.051963103372441</v>
+        <v>-4.031537160755236</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-11.58067451779711</v>
       </c>
       <c r="E58">
-        <v>-8.595398964238539</v>
+        <v>-9.29926420772475</v>
       </c>
       <c r="F58">
-        <v>3.371865243973925</v>
+        <v>2.757198887779482</v>
       </c>
       <c r="G58">
-        <v>-6.854081803173536</v>
+        <v>-4.657167367312244</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-11.46448220907653</v>
       </c>
       <c r="E59">
-        <v>-9.502687788623311</v>
+        <v>-7.903026987783795</v>
       </c>
       <c r="F59">
-        <v>3.653858335571158</v>
+        <v>3.243485291350657</v>
       </c>
       <c r="G59">
-        <v>-6.859434955310537</v>
+        <v>-4.96878901892384</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-11.33870610326402</v>
       </c>
       <c r="E60">
-        <v>-8.812607220016448</v>
+        <v>-6.169893944042204</v>
       </c>
       <c r="F60">
-        <v>3.097480275594464</v>
+        <v>3.087978040101827</v>
       </c>
       <c r="G60">
-        <v>-6.910645784257524</v>
+        <v>-4.321084094710972</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-11.20241838390393</v>
       </c>
       <c r="E61">
-        <v>-8.613807211079719</v>
+        <v>-7.765583273176992</v>
       </c>
       <c r="F61">
-        <v>3.331304951773605</v>
+        <v>2.730353488806868</v>
       </c>
       <c r="G61">
-        <v>-7.263715466020796</v>
+        <v>-5.514764189260445</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-11.05186499301126</v>
       </c>
       <c r="E62">
-        <v>-7.3973639946653</v>
+        <v>-8.12335083367898</v>
       </c>
       <c r="F62">
-        <v>3.487095686381299</v>
+        <v>3.190195171002035</v>
       </c>
       <c r="G62">
-        <v>-7.121689751840522</v>
+        <v>-4.918955376921192</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-10.90131648801133</v>
       </c>
       <c r="E63">
-        <v>-8.413100714585761</v>
+        <v>-7.336786597864693</v>
       </c>
       <c r="F63">
-        <v>3.110330465392339</v>
+        <v>2.705790210058402</v>
       </c>
       <c r="G63">
-        <v>-7.012478165045505</v>
+        <v>-5.917680755208523</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-10.74184766893353</v>
       </c>
       <c r="E64">
-        <v>-7.807571284176111</v>
+        <v>-5.701169713404275</v>
       </c>
       <c r="F64">
-        <v>3.115822757507083</v>
+        <v>2.96329604079111</v>
       </c>
       <c r="G64">
-        <v>-7.39397219080896</v>
+        <v>-5.534710226134554</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-10.57592094092321</v>
       </c>
       <c r="E65">
-        <v>-6.157934244187945</v>
+        <v>-7.10664049184687</v>
       </c>
       <c r="F65">
-        <v>3.176328242006447</v>
+        <v>2.664879918850771</v>
       </c>
       <c r="G65">
-        <v>-7.186016962214101</v>
+        <v>-5.311850921521896</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-10.41184694439919</v>
       </c>
       <c r="E66">
-        <v>-7.800398181347961</v>
+        <v>-7.563124257242065</v>
       </c>
       <c r="F66">
-        <v>3.150699129176891</v>
+        <v>2.445402034559594</v>
       </c>
       <c r="G66">
-        <v>-7.94636981949175</v>
+        <v>-5.565438709830069</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-10.2382403517507</v>
       </c>
       <c r="E67">
-        <v>-8.296909128496955</v>
+        <v>-6.679374440749164</v>
       </c>
       <c r="F67">
-        <v>3.239069919258412</v>
+        <v>2.899287398806794</v>
       </c>
       <c r="G67">
-        <v>-8.310308022260449</v>
+        <v>-4.719521492544417</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-10.06022003647039</v>
       </c>
       <c r="E68">
-        <v>-7.095844609812584</v>
+        <v>-7.136682388413756</v>
       </c>
       <c r="F68">
-        <v>2.743305035783332</v>
+        <v>2.485917982994282</v>
       </c>
       <c r="G68">
-        <v>-7.693795058118594</v>
+        <v>-6.121573944426697</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-9.877557842348658</v>
       </c>
       <c r="E69">
-        <v>-7.542415545604989</v>
+        <v>-7.311839234556437</v>
       </c>
       <c r="F69">
-        <v>2.913979438584326</v>
+        <v>2.211578942086368</v>
       </c>
       <c r="G69">
-        <v>-7.669366542584312</v>
+        <v>-5.409723889844909</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-9.681442627936395</v>
       </c>
       <c r="E70">
-        <v>-7.66884148295113</v>
+        <v>-7.80574630915102</v>
       </c>
       <c r="F70">
-        <v>3.066027876113836</v>
+        <v>2.515314732196669</v>
       </c>
       <c r="G70">
-        <v>-8.12424543131679</v>
+        <v>-5.357294780139472</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-9.483248899664638</v>
       </c>
       <c r="E71">
-        <v>-7.55666212483312</v>
+        <v>-6.010047868519455</v>
       </c>
       <c r="F71">
-        <v>2.838579199950253</v>
+        <v>2.405711196906851</v>
       </c>
       <c r="G71">
-        <v>-7.311589265064196</v>
+        <v>-5.720551010527081</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-9.280913923593776</v>
       </c>
       <c r="E72">
-        <v>-7.812113343605804</v>
+        <v>-7.845931987495087</v>
       </c>
       <c r="F72">
-        <v>2.937367607543536</v>
+        <v>2.257393970514116</v>
       </c>
       <c r="G72">
-        <v>-7.356013475655676</v>
+        <v>-6.00500301489788</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-9.071206153277357</v>
       </c>
       <c r="E73">
-        <v>-7.843676807439267</v>
+        <v>-7.890075552121857</v>
       </c>
       <c r="F73">
-        <v>2.633389510428172</v>
+        <v>2.01738967385293</v>
       </c>
       <c r="G73">
-        <v>-7.45988184195031</v>
+        <v>-5.485502277238827</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-8.864855013251232</v>
       </c>
       <c r="E74">
-        <v>-7.457112680722502</v>
+        <v>-8.027682291792937</v>
       </c>
       <c r="F74">
-        <v>2.535652683562742</v>
+        <v>1.975940922634048</v>
       </c>
       <c r="G74">
-        <v>-7.816745408901586</v>
+        <v>-5.575482904996218</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-8.651537244654513</v>
       </c>
       <c r="E75">
-        <v>-8.067211341405891</v>
+        <v>-7.133987946379191</v>
       </c>
       <c r="F75">
-        <v>2.525743435649838</v>
+        <v>1.95466700107195</v>
       </c>
       <c r="G75">
-        <v>-6.823320214022628</v>
+        <v>-5.083529216769441</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-8.429226499125354</v>
       </c>
       <c r="E76">
-        <v>-9.044397162099054</v>
+        <v>-8.234266747548851</v>
       </c>
       <c r="F76">
-        <v>2.292919661609254</v>
+        <v>1.488195925914753</v>
       </c>
       <c r="G76">
-        <v>-6.781892047144188</v>
+        <v>-5.553146654242755</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-8.19865508288672</v>
       </c>
       <c r="E77">
-        <v>-9.527123434368699</v>
+        <v>-8.58042782916918</v>
       </c>
       <c r="F77">
-        <v>2.505783989997554</v>
+        <v>2.328755759063818</v>
       </c>
       <c r="G77">
-        <v>-6.867175010781353</v>
+        <v>-4.481201940263363</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-7.94681535854237</v>
       </c>
       <c r="E78">
-        <v>-9.779721714516551</v>
+        <v>-8.968780703118975</v>
       </c>
       <c r="F78">
-        <v>2.446803614294759</v>
+        <v>2.022669749375005</v>
       </c>
       <c r="G78">
-        <v>-6.107173071330867</v>
+        <v>-4.837257734103058</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-7.674462630330545</v>
       </c>
       <c r="E79">
-        <v>-9.127607871989998</v>
+        <v>-8.726982833479417</v>
       </c>
       <c r="F79">
-        <v>2.169758019977359</v>
+        <v>2.054777803104624</v>
       </c>
       <c r="G79">
-        <v>-6.057531440969496</v>
+        <v>-4.544446602245599</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-7.37870889310666</v>
       </c>
       <c r="E80">
-        <v>-10.68670713114281</v>
+        <v>-10.84952388561459</v>
       </c>
       <c r="F80">
-        <v>1.776523841173744</v>
+        <v>1.678649231893671</v>
       </c>
       <c r="G80">
-        <v>-6.152477887035793</v>
+        <v>-4.648636091457542</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-7.050972211460492</v>
       </c>
       <c r="E81">
-        <v>-12.12407195202143</v>
+        <v>-11.1823304973863</v>
       </c>
       <c r="F81">
-        <v>2.20589027043811</v>
+        <v>1.47425456274114</v>
       </c>
       <c r="G81">
-        <v>-6.348611157509914</v>
+        <v>-4.113469852306658</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-6.697476161427026</v>
       </c>
       <c r="E82">
-        <v>-12.32039035720195</v>
+        <v>-11.61852669922713</v>
       </c>
       <c r="F82">
-        <v>2.258591252186188</v>
+        <v>1.692536749066159</v>
       </c>
       <c r="G82">
-        <v>-5.901041953328146</v>
+        <v>-4.03874090784869</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-6.315962968143818</v>
       </c>
       <c r="E83">
-        <v>-13.42483082598466</v>
+        <v>-13.44507310479895</v>
       </c>
       <c r="F83">
-        <v>1.903660584653392</v>
+        <v>1.483455894109843</v>
       </c>
       <c r="G83">
-        <v>-4.444769386603683</v>
+        <v>-3.274554438836565</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-5.904058975231194</v>
       </c>
       <c r="E84">
-        <v>-13.99061836850299</v>
+        <v>-14.22501218314001</v>
       </c>
       <c r="F84">
-        <v>2.260353916870072</v>
+        <v>1.374422492949584</v>
       </c>
       <c r="G84">
-        <v>-4.613239738551655</v>
+        <v>-3.681417175067454</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-5.473374867125339</v>
       </c>
       <c r="E85">
-        <v>-14.96746455364558</v>
+        <v>-14.07083575707487</v>
       </c>
       <c r="F85">
-        <v>1.816892504958295</v>
+        <v>1.746159447657023</v>
       </c>
       <c r="G85">
-        <v>-4.807886574078643</v>
+        <v>-2.768709701527006</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-5.024325681892598</v>
       </c>
       <c r="E86">
-        <v>-16.64219839658426</v>
+        <v>-16.92254716545111</v>
       </c>
       <c r="F86">
-        <v>1.924381792851002</v>
+        <v>1.249989135467591</v>
       </c>
       <c r="G86">
-        <v>-3.885416301742884</v>
+        <v>-2.907934694181056</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-4.564247086990277</v>
       </c>
       <c r="E87">
-        <v>-17.38569231611159</v>
+        <v>-19.15915142089149</v>
       </c>
       <c r="F87">
-        <v>1.624402553172123</v>
+        <v>1.282111442550449</v>
       </c>
       <c r="G87">
-        <v>-4.559559242632372</v>
+        <v>-3.456210693667453</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-4.10507135185603</v>
       </c>
       <c r="E88">
-        <v>-19.82299853957192</v>
+        <v>-19.68699035122555</v>
       </c>
       <c r="F88">
-        <v>1.35503951625052</v>
+        <v>0.6712618176122154</v>
       </c>
       <c r="G88">
-        <v>-3.529959716645797</v>
+        <v>-1.426919110096079</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-3.650541043309337</v>
       </c>
       <c r="E89">
-        <v>-20.63281196094158</v>
+        <v>-20.95681974771639</v>
       </c>
       <c r="F89">
-        <v>1.398795726988197</v>
+        <v>0.9662745555402756</v>
       </c>
       <c r="G89">
-        <v>-2.773675519835912</v>
+        <v>-2.392747597359673</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-3.213479906311787</v>
       </c>
       <c r="E90">
-        <v>-21.3490761662608</v>
+        <v>-21.49087174438897</v>
       </c>
       <c r="F90">
-        <v>0.8462454842091199</v>
+        <v>0.8553581280465584</v>
       </c>
       <c r="G90">
-        <v>-3.16324065562411</v>
+        <v>-2.021949944233604</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-2.803611493349925</v>
       </c>
       <c r="E91">
-        <v>-24.03523562186463</v>
+        <v>-23.53251613685112</v>
       </c>
       <c r="F91">
-        <v>1.407667647526489</v>
+        <v>0.9425633105743162</v>
       </c>
       <c r="G91">
-        <v>-3.420450180752246</v>
+        <v>-1.609191126397272</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-2.424900774275617</v>
       </c>
       <c r="E92">
-        <v>-25.64471415435278</v>
+        <v>-27.06298692881505</v>
       </c>
       <c r="F92">
-        <v>1.041432487169285</v>
+        <v>0.02402813297267565</v>
       </c>
       <c r="G92">
-        <v>-3.013603997249052</v>
+        <v>-1.71458565418551</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-2.08980136775216</v>
       </c>
       <c r="E93">
-        <v>-27.14762410801841</v>
+        <v>-27.39922159541057</v>
       </c>
       <c r="F93">
-        <v>0.5855928298224339</v>
+        <v>0.2718496020324713</v>
       </c>
       <c r="G93">
-        <v>-2.419407420587424</v>
+        <v>-1.125765403479658</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-1.801428153835179</v>
       </c>
       <c r="E94">
-        <v>-28.73576447098241</v>
+        <v>-29.57751948376519</v>
       </c>
       <c r="F94">
-        <v>0.1404123051394475</v>
+        <v>0.1516748297570951</v>
       </c>
       <c r="G94">
-        <v>-3.135955139289437</v>
+        <v>-1.178618263014123</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-1.560028637598297</v>
       </c>
       <c r="E95">
-        <v>-31.43106238713373</v>
+        <v>-30.67926777475033</v>
       </c>
       <c r="F95">
-        <v>0.1015703338573796</v>
+        <v>-0.01508465202093239</v>
       </c>
       <c r="G95">
-        <v>-3.142867558375436</v>
+        <v>-0.5017507431458142</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-1.3690169570224</v>
       </c>
       <c r="E96">
-        <v>-33.59987312244228</v>
+        <v>-33.21916204838042</v>
       </c>
       <c r="F96">
-        <v>-0.1065674242262921</v>
+        <v>-0.5091763501963507</v>
       </c>
       <c r="G96">
-        <v>-2.997812695026729</v>
+        <v>-0.7610326697815336</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-1.22136547793272</v>
       </c>
       <c r="E97">
-        <v>-35.22794783344292</v>
+        <v>-35.85257157450591</v>
       </c>
       <c r="F97">
-        <v>-0.5553184138956367</v>
+        <v>-0.1571699956364133</v>
       </c>
       <c r="G97">
-        <v>-3.671521954450573</v>
+        <v>-2.492984295197727</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-1.109940095369092</v>
       </c>
       <c r="E98">
-        <v>-38.04184874809212</v>
+        <v>-36.93832303105896</v>
       </c>
       <c r="F98">
-        <v>-0.7281403219179664</v>
+        <v>-0.7884644720900127</v>
       </c>
       <c r="G98">
-        <v>-3.607317234261947</v>
+        <v>-1.527043249385797</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-1.025699326592652</v>
       </c>
       <c r="E99">
-        <v>-40.04716798630174</v>
+        <v>-39.83281719762267</v>
       </c>
       <c r="F99">
-        <v>-1.244504468235167</v>
+        <v>-0.8553475403108514</v>
       </c>
       <c r="G99">
-        <v>-3.913214952636144</v>
+        <v>-2.398776100786686</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-0.9535622763563624</v>
       </c>
       <c r="E100">
-        <v>-43.46517412628518</v>
+        <v>-42.29306693464286</v>
       </c>
       <c r="F100">
-        <v>-1.457591307304587</v>
+        <v>-1.574775250958656</v>
       </c>
       <c r="G100">
-        <v>-3.583242947100367</v>
+        <v>-2.472909147047586</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-0.8826599863579521</v>
       </c>
       <c r="E101">
-        <v>-45.16318432562328</v>
+        <v>-45.22433004591185</v>
       </c>
       <c r="F101">
-        <v>-1.896025244787802</v>
+        <v>-1.785729630012937</v>
       </c>
       <c r="G101">
-        <v>-3.586063531899826</v>
+        <v>-1.983693279981786</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-0.8004106670734433</v>
       </c>
       <c r="E102">
-        <v>-47.27249996941905</v>
+        <v>-48.04489234582633</v>
       </c>
       <c r="F102">
-        <v>-2.152873837565602</v>
+        <v>-2.199160810356151</v>
       </c>
       <c r="G102">
-        <v>-4.634413987820833</v>
+        <v>-1.640346670467354</v>
       </c>
     </row>
   </sheetData>
